--- a/WhatsAppExcelMonitorElevenLabsV2/scripts/excel/20062026.xlsx
+++ b/WhatsAppExcelMonitorElevenLabsV2/scripts/excel/20062026.xlsx
@@ -1,117 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet sheetId="1" name="Evangelio y Oraciones" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evangelio y Oraciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="24">
-  <si>
-    <t>NOMBRES</t>
-  </si>
-  <si>
-    <t>APELLIDO_PATERNO</t>
-  </si>
-  <si>
-    <t>APELLIDO_MATERNO</t>
-  </si>
-  <si>
-    <t>CELULAR</t>
-  </si>
-  <si>
-    <t>MAIL</t>
-  </si>
-  <si>
-    <t>CORREO</t>
-  </si>
-  <si>
-    <t>SMS</t>
-  </si>
-  <si>
-    <t>WHATSAPP</t>
-  </si>
-  <si>
-    <t>TEXTO_MENSAJE</t>
-  </si>
-  <si>
-    <t>Alejandro</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>56994148421</t>
-  </si>
-  <si>
-    <t>lucesalejandro3@gmail.com</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>SI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sábado, 20 de junio de 2026
-*Evangelio del Día*
-Lectura del santo evangelio según san Mateo
-Mateo 6, 24-34 En aquel tiempo, Jesús dijo a sus discípulos: “Nadie puede servir a dos amos, porque odiará a uno y amará al otro, o bien obedecerá al primero y no hará caso al segundo. En resumen, no pueden ustedes servir a Dios y al dinero. Por eso les digo que no se preocupen por su vida, pensando qué comerán o con qué se vestirán. ¿Acaso no vale más la vida que el alimento, y el cuerpo más que el vestido? Miren las aves del cielo, que ni siembran, ni cosechan, ni guardan en graneros y, sin embargo, el Padre celestial las alimenta. ¿Acaso no valen ustedes más que ellas? ¿Quién de ustedes, a fuerza de preocuparse, puede prolongar su vida siquiera un momento? ¿Y por qué se preocupan del vestido? Miren cómo crecen los lirios del campo, que no trabajan ni hilan. Pues bien, yo les aseguro que ni Salomón, en todo el esplendor de su gloria, se vestía como uno de ellos. Y si Dios viste así a la hierba del campo, que hoy florece y mañana es echada al horno, ¿no hará mucho más por ustedes, hombres de poca fe? No se inquieten, pues, pensando: ¿Qué comeremos o qué beberemos o con qué nos vestiremos? Los que no conocen a Dios se desviven por todas estas cosas; pero el Padre celestial ya sabe que ustedes tienen necesidad de ellas. Por consiguiente, busquen primero el Reino de Dios y su justicia, y todas estas cosas se les darán por añadidura. No se preocupen por el día de mañana, porque el día de mañana traerá ya sus propias preocupaciones. A cada día le bastan sus propios problemas”.
-*Oración de la mañana*
-Querido Jesús, me despierto hoy recordando tus palabras, reconociendo que no puedo servir a dos amos. Ayúdame a elegirte a ti por encima de todo, incluso por encima de mis preocupaciones mundanas. Que mi corazón esté fijado en ti y en tu reino, antes que en el dinero y las posesiones.
-Padre celestial, gracias por un nuevo día. En la sencillez de la naturaleza, me recuerdas que cuidas incluso de las aves y los lirios del campo. Que no me consuma la preocupación por lo que comeré o cómo me vestiré, sino que confíe en tu amor y en tu provisión. Me recuerdas, Padre, que valgo más que muchos pájaros y que tu cuidado por mí es infinito.
-Espíritu Santo, guíame hoy para buscar primero el Reino de Dios y su justicia. Que en cada momento y en cada tarea, pueda ver tu presencia y tu obra. Líbrame de la ansiedad por el mañana y permíteme vivir plenamente el hoy, sabiendo que cada día trae sus propias bendiciones y desafíos.
-Amén.</t>
-  </si>
-  <si>
-    <t>Omar</t>
-  </si>
-  <si>
-    <t>56973223070</t>
-  </si>
-  <si>
-    <t>Mama</t>
-  </si>
-  <si>
-    <t>56971748545</t>
-  </si>
-  <si>
-    <t>Victor</t>
-  </si>
-  <si>
-    <t>56931123918</t>
-  </si>
-  <si>
-    <t>Yume</t>
-  </si>
-  <si>
-    <t>584146711206</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
-      <family val="2"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -135,28 +51,87 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -481,193 +456,491 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="8" width="5" customWidth="1"/>
-    <col min="9" max="9" width="100" style="1" customWidth="1"/>
+    <col width="20" customWidth="1" min="1" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="8"/>
+    <col width="100" customWidth="1" style="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="1" s="2">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>NOMBRES</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>APELLIDO_PATERNO</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>APELLIDO_MATERNO</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>CELULAR</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>MAIL</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>CORREO</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>SMS</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>WHATSAPP</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>TEXTO_MENSAJE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="150" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>56994148421</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>sábado, 20 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 24-34 En aquel tiempo, Jesús dijo a sus discípulos: “Nadie puede servir a dos amos, porque odiará a uno y amará al otro, o bien obedecerá al primero y no hará caso al segundo. En resumen, no pueden ustedes servir a Dios y al dinero. Por eso les digo que no se preocupen por su vida, pensando qué comerán o con qué se vestirán. ¿Acaso no vale más la vida que el alimento, y el cuerpo más que el vestido? Miren las aves del cielo, que ni siembran, ni cosechan, ni guardan en graneros y, sin embargo, el Padre celestial las alimenta. ¿Acaso no valen ustedes más que ellas? ¿Quién de ustedes, a fuerza de preocuparse, puede prolongar su vida siquiera un momento? ¿Y por qué se preocupan del vestido? Miren cómo crecen los lirios del campo, que no trabajan ni hilan. Pues bien, yo les aseguro que ni Salomón, en todo el esplendor de su gloria, se vestía como uno de ellos. Y si Dios viste así a la hierba del campo, que hoy florece y mañana es echada al horno, ¿no hará mucho más por ustedes, hombres de poca fe? No se inquieten, pues, pensando: ¿Qué comeremos o qué beberemos o con qué nos vestiremos? Los que no conocen a Dios se desviven por todas estas cosas; pero el Padre celestial ya sabe que ustedes tienen necesidad de ellas. Por consiguiente, busquen primero el Reino de Dios y su justicia, y todas estas cosas se les darán por añadidura. No se preocupen por el día de mañana, porque el día de mañana traerá ya sus propias preocupaciones. A cada día le bastan sus propios problemas”.
+*Oración de la mañana*
+Querido Jesús, me despierto hoy recordando tus palabras, reconociendo que no puedo servir a dos amos. Ayúdame a elegirte a ti por encima de todo, incluso por encima de mis preocupaciones mundanas. Que mi corazón esté fijado en ti y en tu reino, antes que en el dinero y las posesiones.
+Padre celestial, gracias por un nuevo día. En la sencillez de la naturaleza, me recuerdas que cuidas incluso de las aves y los lirios del campo. Que no me consuma la preocupación por lo que comeré o cómo me vestiré, sino que confíe en tu amor y en tu provisión. Me recuerdas, Padre, que valgo más que muchos pájaros y que tu cuidado por mí es infinito.
+Espíritu Santo, guíame hoy para buscar primero el Reino de Dios y su justicia. Que en cada momento y en cada tarea, pueda ver tu presencia y tu obra. Líbrame de la ansiedad por el mañana y permíteme vivir plenamente el hoy, sabiendo que cada día trae sus propias bendiciones y desafíos.
+Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="2" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2">
+    <row r="3" ht="150" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Omar</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>56973223070</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>15</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>sábado, 20 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 24-34 En aquel tiempo, Jesús dijo a sus discípulos: “Nadie puede servir a dos amos, porque odiará a uno y amará al otro, o bien obedecerá al primero y no hará caso al segundo. En resumen, no pueden ustedes servir a Dios y al dinero. Por eso les digo que no se preocupen por su vida, pensando qué comerán o con qué se vestirán. ¿Acaso no vale más la vida que el alimento, y el cuerpo más que el vestido? Miren las aves del cielo, que ni siembran, ni cosechan, ni guardan en graneros y, sin embargo, el Padre celestial las alimenta. ¿Acaso no valen ustedes más que ellas? ¿Quién de ustedes, a fuerza de preocuparse, puede prolongar su vida siquiera un momento? ¿Y por qué se preocupan del vestido? Miren cómo crecen los lirios del campo, que no trabajan ni hilan. Pues bien, yo les aseguro que ni Salomón, en todo el esplendor de su gloria, se vestía como uno de ellos. Y si Dios viste así a la hierba del campo, que hoy florece y mañana es echada al horno, ¿no hará mucho más por ustedes, hombres de poca fe? No se inquieten, pues, pensando: ¿Qué comeremos o qué beberemos o con qué nos vestiremos? Los que no conocen a Dios se desviven por todas estas cosas; pero el Padre celestial ya sabe que ustedes tienen necesidad de ellas. Por consiguiente, busquen primero el Reino de Dios y su justicia, y todas estas cosas se les darán por añadidura. No se preocupen por el día de mañana, porque el día de mañana traerá ya sus propias preocupaciones. A cada día le bastan sus propios problemas”.
+*Oración de la mañana*
+Querido Jesús, me despierto hoy recordando tus palabras, reconociendo que no puedo servir a dos amos. Ayúdame a elegirte a ti por encima de todo, incluso por encima de mis preocupaciones mundanas. Que mi corazón esté fijado en ti y en tu reino, antes que en el dinero y las posesiones.
+Padre celestial, gracias por un nuevo día. En la sencillez de la naturaleza, me recuerdas que cuidas incluso de las aves y los lirios del campo. Que no me consuma la preocupación por lo que comeré o cómo me vestiré, sino que confíe en tu amor y en tu provisión. Me recuerdas, Padre, que valgo más que muchos pájaros y que tu cuidado por mí es infinito.
+Espíritu Santo, guíame hoy para buscar primero el Reino de Dios y su justicia. Que en cada momento y en cada tarea, pueda ver tu presencia y tu obra. Líbrame de la ansiedad por el mañana y permíteme vivir plenamente el hoy, sabiendo que cada día trae sus propias bendiciones y desafíos.
+Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="3" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
+    <row r="4" ht="150" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Mama</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>56971748545</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>15</v>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>sábado, 20 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 24-34 En aquel tiempo, Jesús dijo a sus discípulos: “Nadie puede servir a dos amos, porque odiará a uno y amará al otro, o bien obedecerá al primero y no hará caso al segundo. En resumen, no pueden ustedes servir a Dios y al dinero. Por eso les digo que no se preocupen por su vida, pensando qué comerán o con qué se vestirán. ¿Acaso no vale más la vida que el alimento, y el cuerpo más que el vestido? Miren las aves del cielo, que ni siembran, ni cosechan, ni guardan en graneros y, sin embargo, el Padre celestial las alimenta. ¿Acaso no valen ustedes más que ellas? ¿Quién de ustedes, a fuerza de preocuparse, puede prolongar su vida siquiera un momento? ¿Y por qué se preocupan del vestido? Miren cómo crecen los lirios del campo, que no trabajan ni hilan. Pues bien, yo les aseguro que ni Salomón, en todo el esplendor de su gloria, se vestía como uno de ellos. Y si Dios viste así a la hierba del campo, que hoy florece y mañana es echada al horno, ¿no hará mucho más por ustedes, hombres de poca fe? No se inquieten, pues, pensando: ¿Qué comeremos o qué beberemos o con qué nos vestiremos? Los que no conocen a Dios se desviven por todas estas cosas; pero el Padre celestial ya sabe que ustedes tienen necesidad de ellas. Por consiguiente, busquen primero el Reino de Dios y su justicia, y todas estas cosas se les darán por añadidura. No se preocupen por el día de mañana, porque el día de mañana traerá ya sus propias preocupaciones. A cada día le bastan sus propios problemas”.
+*Oración de la mañana*
+Querido Jesús, me despierto hoy recordando tus palabras, reconociendo que no puedo servir a dos amos. Ayúdame a elegirte a ti por encima de todo, incluso por encima de mis preocupaciones mundanas. Que mi corazón esté fijado en ti y en tu reino, antes que en el dinero y las posesiones.
+Padre celestial, gracias por un nuevo día. En la sencillez de la naturaleza, me recuerdas que cuidas incluso de las aves y los lirios del campo. Que no me consuma la preocupación por lo que comeré o cómo me vestiré, sino que confíe en tu amor y en tu provisión. Me recuerdas, Padre, que valgo más que muchos pájaros y que tu cuidado por mí es infinito.
+Espíritu Santo, guíame hoy para buscar primero el Reino de Dios y su justicia. Que en cada momento y en cada tarea, pueda ver tu presencia y tu obra. Líbrame de la ansiedad por el mañana y permíteme vivir plenamente el hoy, sabiendo que cada día trae sus propias bendiciones y desafíos.
+Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="4" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4">
+    <row r="5" ht="150" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Victor</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>56931123918</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>15</v>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>sábado, 20 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 24-34 En aquel tiempo, Jesús dijo a sus discípulos: “Nadie puede servir a dos amos, porque odiará a uno y amará al otro, o bien obedecerá al primero y no hará caso al segundo. En resumen, no pueden ustedes servir a Dios y al dinero. Por eso les digo que no se preocupen por su vida, pensando qué comerán o con qué se vestirán. ¿Acaso no vale más la vida que el alimento, y el cuerpo más que el vestido? Miren las aves del cielo, que ni siembran, ni cosechan, ni guardan en graneros y, sin embargo, el Padre celestial las alimenta. ¿Acaso no valen ustedes más que ellas? ¿Quién de ustedes, a fuerza de preocuparse, puede prolongar su vida siquiera un momento? ¿Y por qué se preocupan del vestido? Miren cómo crecen los lirios del campo, que no trabajan ni hilan. Pues bien, yo les aseguro que ni Salomón, en todo el esplendor de su gloria, se vestía como uno de ellos. Y si Dios viste así a la hierba del campo, que hoy florece y mañana es echada al horno, ¿no hará mucho más por ustedes, hombres de poca fe? No se inquieten, pues, pensando: ¿Qué comeremos o qué beberemos o con qué nos vestiremos? Los que no conocen a Dios se desviven por todas estas cosas; pero el Padre celestial ya sabe que ustedes tienen necesidad de ellas. Por consiguiente, busquen primero el Reino de Dios y su justicia, y todas estas cosas se les darán por añadidura. No se preocupen por el día de mañana, porque el día de mañana traerá ya sus propias preocupaciones. A cada día le bastan sus propios problemas”.
+*Oración de la mañana*
+Querido Jesús, me despierto hoy recordando tus palabras, reconociendo que no puedo servir a dos amos. Ayúdame a elegirte a ti por encima de todo, incluso por encima de mis preocupaciones mundanas. Que mi corazón esté fijado en ti y en tu reino, antes que en el dinero y las posesiones.
+Padre celestial, gracias por un nuevo día. En la sencillez de la naturaleza, me recuerdas que cuidas incluso de las aves y los lirios del campo. Que no me consuma la preocupación por lo que comeré o cómo me vestiré, sino que confíe en tu amor y en tu provisión. Me recuerdas, Padre, que valgo más que muchos pájaros y que tu cuidado por mí es infinito.
+Espíritu Santo, guíame hoy para buscar primero el Reino de Dios y su justicia. Que en cada momento y en cada tarea, pueda ver tu presencia y tu obra. Líbrame de la ansiedad por el mañana y permíteme vivir plenamente el hoy, sabiendo que cada día trae sus propias bendiciones y desafíos.
+Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="5" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5">
+    <row r="6" ht="150" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Yume</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>584146711206</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>15</v>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>sábado, 20 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 24-34 En aquel tiempo, Jesús dijo a sus discípulos: “Nadie puede servir a dos amos, porque odiará a uno y amará al otro, o bien obedecerá al primero y no hará caso al segundo. En resumen, no pueden ustedes servir a Dios y al dinero. Por eso les digo que no se preocupen por su vida, pensando qué comerán o con qué se vestirán. ¿Acaso no vale más la vida que el alimento, y el cuerpo más que el vestido? Miren las aves del cielo, que ni siembran, ni cosechan, ni guardan en graneros y, sin embargo, el Padre celestial las alimenta. ¿Acaso no valen ustedes más que ellas? ¿Quién de ustedes, a fuerza de preocuparse, puede prolongar su vida siquiera un momento? ¿Y por qué se preocupan del vestido? Miren cómo crecen los lirios del campo, que no trabajan ni hilan. Pues bien, yo les aseguro que ni Salomón, en todo el esplendor de su gloria, se vestía como uno de ellos. Y si Dios viste así a la hierba del campo, que hoy florece y mañana es echada al horno, ¿no hará mucho más por ustedes, hombres de poca fe? No se inquieten, pues, pensando: ¿Qué comeremos o qué beberemos o con qué nos vestiremos? Los que no conocen a Dios se desviven por todas estas cosas; pero el Padre celestial ya sabe que ustedes tienen necesidad de ellas. Por consiguiente, busquen primero el Reino de Dios y su justicia, y todas estas cosas se les darán por añadidura. No se preocupen por el día de mañana, porque el día de mañana traerá ya sus propias preocupaciones. A cada día le bastan sus propios problemas”.
+*Oración de la mañana*
+Querido Jesús, me despierto hoy recordando tus palabras, reconociendo que no puedo servir a dos amos. Ayúdame a elegirte a ti por encima de todo, incluso por encima de mis preocupaciones mundanas. Que mi corazón esté fijado en ti y en tu reino, antes que en el dinero y las posesiones.
+Padre celestial, gracias por un nuevo día. En la sencillez de la naturaleza, me recuerdas que cuidas incluso de las aves y los lirios del campo. Que no me consuma la preocupación por lo que comeré o cómo me vestiré, sino que confíe en tu amor y en tu provisión. Me recuerdas, Padre, que valgo más que muchos pájaros y que tu cuidado por mí es infinito.
+Espíritu Santo, guíame hoy para buscar primero el Reino de Dios y su justicia. Que en cada momento y en cada tarea, pueda ver tu presencia y tu obra. Líbrame de la ansiedad por el mañana y permíteme vivir plenamente el hoy, sabiendo que cada día trae sus propias bendiciones y desafíos.
+Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="6" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Mariangely</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>González</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>56972028078</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>mariangelygonzalez14@gmail.com</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>15</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>sábado, 20 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 24-34 En aquel tiempo, Jesús dijo a sus discípulos: “Nadie puede servir a dos amos, porque odiará a uno y amará al otro, o bien obedecerá al primero y no hará caso al segundo. En resumen, no pueden ustedes servir a Dios y al dinero. Por eso les digo que no se preocupen por su vida, pensando qué comerán o con qué se vestirán. ¿Acaso no vale más la vida que el alimento, y el cuerpo más que el vestido? Miren las aves del cielo, que ni siembran, ni cosechan, ni guardan en graneros y, sin embargo, el Padre celestial las alimenta. ¿Acaso no valen ustedes más que ellas? ¿Quién de ustedes, a fuerza de preocuparse, puede prolongar su vida siquiera un momento? ¿Y por qué se preocupan del vestido? Miren cómo crecen los lirios del campo, que no trabajan ni hilan. Pues bien, yo les aseguro que ni Salomón, en todo el esplendor de su gloria, se vestía como uno de ellos. Y si Dios viste así a la hierba del campo, que hoy florece y mañana es echada al horno, ¿no hará mucho más por ustedes, hombres de poca fe? No se inquieten, pues, pensando: ¿Qué comeremos o qué beberemos o con qué nos vestiremos? Los que no conocen a Dios se desviven por todas estas cosas; pero el Padre celestial ya sabe que ustedes tienen necesidad de ellas. Por consiguiente, busquen primero el Reino de Dios y su justicia, y todas estas cosas se les darán por añadidura. No se preocupen por el día de mañana, porque el día de mañana traerá ya sus propias preocupaciones. A cada día le bastan sus propios problemas”.
+*Oración de la mañana*
+Querido Jesús, me despierto hoy recordando tus palabras, reconociendo que no puedo servir a dos amos. Ayúdame a elegirte a ti por encima de todo, incluso por encima de mis preocupaciones mundanas. Que mi corazón esté fijado en ti y en tu reino, antes que en el dinero y las posesiones.
+Padre celestial, gracias por un nuevo día. En la sencillez de la naturaleza, me recuerdas que cuidas incluso de las aves y los lirios del campo. Que no me consuma la preocupación por lo que comeré o cómo me vestiré, sino que confíe en tu amor y en tu provisión. Me recuerdas, Padre, que valgo más que muchos pájaros y que tu cuidado por mí es infinito.
+Espíritu Santo, guíame hoy para buscar primero el Reino de Dios y su justicia. Que en cada momento y en cada tarea, pueda ver tu presencia y tu obra. Líbrame de la ansiedad por el mañana y permíteme vivir plenamente el hoy, sabiendo que cada día trae sus propias bendiciones y desafíos.
+Amén.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ALEJANDRO MANUEL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LUCES</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>34672527995</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>alejandroluces5515@gmail.com</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>sábado, 20 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 24-34 En aquel tiempo, Jesús dijo a sus discípulos: “Nadie puede servir a dos amos, porque odiará a uno y amará al otro, o bien obedecerá al primero y no hará caso al segundo. En resumen, no pueden ustedes servir a Dios y al dinero. Por eso les digo que no se preocupen por su vida, pensando qué comerán o con qué se vestirán. ¿Acaso no vale más la vida que el alimento, y el cuerpo más que el vestido? Miren las aves del cielo, que ni siembran, ni cosechan, ni guardan en graneros y, sin embargo, el Padre celestial las alimenta. ¿Acaso no valen ustedes más que ellas? ¿Quién de ustedes, a fuerza de preocuparse, puede prolongar su vida siquiera un momento? ¿Y por qué se preocupan del vestido? Miren cómo crecen los lirios del campo, que no trabajan ni hilan. Pues bien, yo les aseguro que ni Salomón, en todo el esplendor de su gloria, se vestía como uno de ellos. Y si Dios viste así a la hierba del campo, que hoy florece y mañana es echada al horno, ¿no hará mucho más por ustedes, hombres de poca fe? No se inquieten, pues, pensando: ¿Qué comeremos o qué beberemos o con qué nos vestiremos? Los que no conocen a Dios se desviven por todas estas cosas; pero el Padre celestial ya sabe que ustedes tienen necesidad de ellas. Por consiguiente, busquen primero el Reino de Dios y su justicia, y todas estas cosas se les darán por añadidura. No se preocupen por el día de mañana, porque el día de mañana traerá ya sus propias preocupaciones. A cada día le bastan sus propios problemas”.
+*Oración de la mañana*
+Querido Jesús, me despierto hoy recordando tus palabras, reconociendo que no puedo servir a dos amos. Ayúdame a elegirte a ti por encima de todo, incluso por encima de mis preocupaciones mundanas. Que mi corazón esté fijado en ti y en tu reino, antes que en el dinero y las posesiones.
+Padre celestial, gracias por un nuevo día. En la sencillez de la naturaleza, me recuerdas que cuidas incluso de las aves y los lirios del campo. Que no me consuma la preocupación por lo que comeré o cómo me vestiré, sino que confíe en tu amor y en tu provisión. Me recuerdas, Padre, que valgo más que muchos pájaros y que tu cuidado por mí es infinito.
+Espíritu Santo, guíame hoy para buscar primero el Reino de Dios y su justicia. Que en cada momento y en cada tarea, pueda ver tu presencia y tu obra. Líbrame de la ansiedad por el mañana y permíteme vivir plenamente el hoy, sabiendo que cada día trae sus propias bendiciones y desafíos.
+Amén.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Marianny</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Gonzalez</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>56967970252</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>marikaro2508@gmail.com</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>sábado, 20 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 24-34 En aquel tiempo, Jesús dijo a sus discípulos: “Nadie puede servir a dos amos, porque odiará a uno y amará al otro, o bien obedecerá al primero y no hará caso al segundo. En resumen, no pueden ustedes servir a Dios y al dinero. Por eso les digo que no se preocupen por su vida, pensando qué comerán o con qué se vestirán. ¿Acaso no vale más la vida que el alimento, y el cuerpo más que el vestido? Miren las aves del cielo, que ni siembran, ni cosechan, ni guardan en graneros y, sin embargo, el Padre celestial las alimenta. ¿Acaso no valen ustedes más que ellas? ¿Quién de ustedes, a fuerza de preocuparse, puede prolongar su vida siquiera un momento? ¿Y por qué se preocupan del vestido? Miren cómo crecen los lirios del campo, que no trabajan ni hilan. Pues bien, yo les aseguro que ni Salomón, en todo el esplendor de su gloria, se vestía como uno de ellos. Y si Dios viste así a la hierba del campo, que hoy florece y mañana es echada al horno, ¿no hará mucho más por ustedes, hombres de poca fe? No se inquieten, pues, pensando: ¿Qué comeremos o qué beberemos o con qué nos vestiremos? Los que no conocen a Dios se desviven por todas estas cosas; pero el Padre celestial ya sabe que ustedes tienen necesidad de ellas. Por consiguiente, busquen primero el Reino de Dios y su justicia, y todas estas cosas se les darán por añadidura. No se preocupen por el día de mañana, porque el día de mañana traerá ya sus propias preocupaciones. A cada día le bastan sus propios problemas”.
+*Oración de la mañana*
+Querido Jesús, me despierto hoy recordando tus palabras, reconociendo que no puedo servir a dos amos. Ayúdame a elegirte a ti por encima de todo, incluso por encima de mis preocupaciones mundanas. Que mi corazón esté fijado en ti y en tu reino, antes que en el dinero y las posesiones.
+Padre celestial, gracias por un nuevo día. En la sencillez de la naturaleza, me recuerdas que cuidas incluso de las aves y los lirios del campo. Que no me consuma la preocupación por lo que comeré o cómo me vestiré, sino que confíe en tu amor y en tu provisión. Me recuerdas, Padre, que valgo más que muchos pájaros y que tu cuidado por mí es infinito.
+Espíritu Santo, guíame hoy para buscar primero el Reino de Dios y su justicia. Que en cada momento y en cada tarea, pueda ver tu presencia y tu obra. Líbrame de la ansiedad por el mañana y permíteme vivir plenamente el hoy, sabiendo que cada día trae sus propias bendiciones y desafíos.
+Amén.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Milagros</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>González</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>56936637515</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Milagrosghurtado@gmail.com</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>sábado, 20 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 24-34 En aquel tiempo, Jesús dijo a sus discípulos: “Nadie puede servir a dos amos, porque odiará a uno y amará al otro, o bien obedecerá al primero y no hará caso al segundo. En resumen, no pueden ustedes servir a Dios y al dinero. Por eso les digo que no se preocupen por su vida, pensando qué comerán o con qué se vestirán. ¿Acaso no vale más la vida que el alimento, y el cuerpo más que el vestido? Miren las aves del cielo, que ni siembran, ni cosechan, ni guardan en graneros y, sin embargo, el Padre celestial las alimenta. ¿Acaso no valen ustedes más que ellas? ¿Quién de ustedes, a fuerza de preocuparse, puede prolongar su vida siquiera un momento? ¿Y por qué se preocupan del vestido? Miren cómo crecen los lirios del campo, que no trabajan ni hilan. Pues bien, yo les aseguro que ni Salomón, en todo el esplendor de su gloria, se vestía como uno de ellos. Y si Dios viste así a la hierba del campo, que hoy florece y mañana es echada al horno, ¿no hará mucho más por ustedes, hombres de poca fe? No se inquieten, pues, pensando: ¿Qué comeremos o qué beberemos o con qué nos vestiremos? Los que no conocen a Dios se desviven por todas estas cosas; pero el Padre celestial ya sabe que ustedes tienen necesidad de ellas. Por consiguiente, busquen primero el Reino de Dios y su justicia, y todas estas cosas se les darán por añadidura. No se preocupen por el día de mañana, porque el día de mañana traerá ya sus propias preocupaciones. A cada día le bastan sus propios problemas”.
+*Oración de la mañana*
+Querido Jesús, me despierto hoy recordando tus palabras, reconociendo que no puedo servir a dos amos. Ayúdame a elegirte a ti por encima de todo, incluso por encima de mis preocupaciones mundanas. Que mi corazón esté fijado en ti y en tu reino, antes que en el dinero y las posesiones.
+Padre celestial, gracias por un nuevo día. En la sencillez de la naturaleza, me recuerdas que cuidas incluso de las aves y los lirios del campo. Que no me consuma la preocupación por lo que comeré o cómo me vestiré, sino que confíe en tu amor y en tu provisión. Me recuerdas, Padre, que valgo más que muchos pájaros y que tu cuidado por mí es infinito.
+Espíritu Santo, guíame hoy para buscar primero el Reino de Dios y su justicia. Que en cada momento y en cada tarea, pueda ver tu presencia y tu obra. Líbrame de la ansiedad por el mañana y permíteme vivir plenamente el hoy, sabiendo que cada día trae sus propias bendiciones y desafíos.
+Amén.</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>